--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aledi\OneDrive\Documents\GitHub\Chen2010housing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C88BABA-D895-4358-8E36-A4A28F9F245D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B330ADC5-2FF9-4B87-8C74-49F07F9B9C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12096" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Grid sizes</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>ngridinterp</t>
+  </si>
+  <si>
+    <t>level1n</t>
   </si>
 </sst>
 </file>
@@ -126,14 +129,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -424,23 +428,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -451,8 +455,14 @@
       <c r="B4">
         <v>401</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="5">
         <v>13.982047</v>
+      </c>
+      <c r="D4" s="5">
+        <v>6.95</v>
+      </c>
+      <c r="E4" s="5">
+        <v>7.4343000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -481,9 +491,17 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
         <v>9</v>
       </c>
-      <c r="B8">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
         <v>15</v>
       </c>
     </row>
